--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -1452,7 +1452,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124893402</v>
+        <v>124891215</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1507,14 +1507,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477929</v>
+        <v>477827</v>
       </c>
       <c r="R8" t="n">
-        <v>6600947</v>
+        <v>6601000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,7 +1583,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891215</v>
+        <v>124893402</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1638,14 +1638,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477827</v>
+        <v>477929</v>
       </c>
       <c r="R9" t="n">
-        <v>6601000</v>
+        <v>6600947</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124891336</v>
+        <v>124893662</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -725,19 +725,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477824</v>
+        <v>477909</v>
       </c>
       <c r="R2" t="n">
-        <v>6601003</v>
+        <v>6600929</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,12 +779,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tappade yttre vingpennor, slagsmål?</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,7 +806,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124893740</v>
+        <v>124893754</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -861,19 +856,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477877</v>
+        <v>477867</v>
       </c>
       <c r="R3" t="n">
-        <v>6600884</v>
+        <v>6600886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -905,7 +901,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -915,7 +911,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -942,10 +938,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124892816</v>
+        <v>124891352</v>
       </c>
       <c r="B4" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -958,34 +954,53 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477914</v>
+        <v>477836</v>
       </c>
       <c r="R4" t="n">
-        <v>6601027</v>
+        <v>6601000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,12 +1042,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På torkad rönn.</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1069,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893662</v>
+        <v>124892509</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1109,7 +1119,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1118,10 +1128,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477909</v>
+        <v>477884</v>
       </c>
       <c r="R5" t="n">
-        <v>6600929</v>
+        <v>6601095</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,7 +1163,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,7 +1173,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124892723</v>
+        <v>124892816</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1206,53 +1216,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477910</v>
+        <v>477914</v>
       </c>
       <c r="R6" t="n">
-        <v>6601063</v>
+        <v>6601027</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1275,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1285,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På torkad rönn.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1321,7 +1317,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124892467</v>
+        <v>124893715</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1376,14 +1372,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477876</v>
+        <v>477879</v>
       </c>
       <c r="R7" t="n">
-        <v>6601108</v>
+        <v>6600886</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,7 +1411,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1425,7 +1421,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1452,7 +1448,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124891215</v>
+        <v>124893740</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1502,7 +1498,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1511,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477827</v>
+        <v>477877</v>
       </c>
       <c r="R8" t="n">
-        <v>6601000</v>
+        <v>6600884</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1556,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,7 +1579,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124893402</v>
+        <v>124891336</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1633,19 +1629,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477929</v>
+        <v>477824</v>
       </c>
       <c r="R9" t="n">
-        <v>6600947</v>
+        <v>6601003</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1677,7 +1673,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1687,7 +1683,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tappade yttre vingpennor, slagsmål?</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1714,7 +1715,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124893754</v>
+        <v>124893402</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1767,17 +1768,16 @@
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477867</v>
+        <v>477929</v>
       </c>
       <c r="R10" t="n">
-        <v>6600886</v>
+        <v>6600947</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1846,7 +1846,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124892509</v>
+        <v>124892723</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477884</v>
+        <v>477910</v>
       </c>
       <c r="R11" t="n">
-        <v>6601095</v>
+        <v>6601063</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1977,7 +1977,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124893715</v>
+        <v>124892467</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -2032,14 +2032,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477879</v>
+        <v>477876</v>
       </c>
       <c r="R12" t="n">
-        <v>6600886</v>
+        <v>6601108</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124891352</v>
+        <v>124891215</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2167,7 +2167,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477836</v>
+        <v>477827</v>
       </c>
       <c r="R13" t="n">
         <v>6601000</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124893662</v>
+        <v>124891336</v>
       </c>
       <c r="B2" t="n">
         <v>56722</v>
@@ -725,19 +725,19 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477909</v>
+        <v>477824</v>
       </c>
       <c r="R2" t="n">
-        <v>6600929</v>
+        <v>6601003</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +769,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,7 +779,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tappade yttre vingpennor, slagsmål?</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -938,7 +943,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124891352</v>
+        <v>124892509</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -993,14 +998,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477836</v>
+        <v>477884</v>
       </c>
       <c r="R4" t="n">
-        <v>6601000</v>
+        <v>6601095</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1032,7 +1037,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1042,7 +1047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1069,7 +1074,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124892509</v>
+        <v>124893402</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1119,7 +1124,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1128,10 +1133,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477884</v>
+        <v>477929</v>
       </c>
       <c r="R5" t="n">
-        <v>6601095</v>
+        <v>6600947</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1163,7 +1168,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1173,7 +1178,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1317,7 +1322,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124893715</v>
+        <v>124891215</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1367,7 +1372,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1376,10 +1381,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477879</v>
+        <v>477827</v>
       </c>
       <c r="R7" t="n">
-        <v>6600886</v>
+        <v>6601000</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1416,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1421,7 +1426,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,7 +1453,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124893740</v>
+        <v>124892723</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1498,19 +1503,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477877</v>
+        <v>477910</v>
       </c>
       <c r="R8" t="n">
-        <v>6600884</v>
+        <v>6601063</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1547,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1557,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,7 +1584,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891336</v>
+        <v>124893662</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1629,19 +1634,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477824</v>
+        <v>477909</v>
       </c>
       <c r="R9" t="n">
-        <v>6601003</v>
+        <v>6600929</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1673,7 +1678,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1683,12 +1688,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tappade yttre vingpennor, slagsmål?</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1715,7 +1715,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124893402</v>
+        <v>124893740</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1765,19 +1765,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477929</v>
+        <v>477877</v>
       </c>
       <c r="R10" t="n">
-        <v>6600947</v>
+        <v>6600884</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1846,7 +1846,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124892723</v>
+        <v>124891352</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1896,19 +1896,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477910</v>
+        <v>477836</v>
       </c>
       <c r="R11" t="n">
-        <v>6601063</v>
+        <v>6601000</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124891215</v>
+        <v>124893715</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477827</v>
+        <v>477879</v>
       </c>
       <c r="R13" t="n">
-        <v>6601000</v>
+        <v>6600886</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124891336</v>
+        <v>124892816</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>79920</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,53 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>477824</v>
+        <v>477914</v>
       </c>
       <c r="R2" t="n">
-        <v>6601003</v>
+        <v>6601027</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -769,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -779,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Tappade yttre vingpennor, slagsmål?</t>
+          <t>På torkad rönn.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -811,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124893754</v>
+        <v>124891352</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -861,20 +842,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477867</v>
+        <v>477836</v>
       </c>
       <c r="R3" t="n">
-        <v>6600886</v>
+        <v>6601000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -906,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -943,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124892509</v>
+        <v>124891215</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -993,19 +973,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477884</v>
+        <v>477827</v>
       </c>
       <c r="R4" t="n">
-        <v>6601095</v>
+        <v>6601000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1037,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1047,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,7 +1054,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893402</v>
+        <v>124892509</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1124,7 +1104,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1133,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477929</v>
+        <v>477884</v>
       </c>
       <c r="R5" t="n">
-        <v>6600947</v>
+        <v>6601095</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1168,7 +1148,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1178,7 +1158,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1205,10 +1185,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124892816</v>
+        <v>124893754</v>
       </c>
       <c r="B6" t="n">
-        <v>79920</v>
+        <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1221,34 +1201,54 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477914</v>
+        <v>477867</v>
       </c>
       <c r="R6" t="n">
-        <v>6601027</v>
+        <v>6600886</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1290,12 +1290,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På torkad rönn.</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1322,7 +1317,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124891215</v>
+        <v>124893402</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1377,14 +1372,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477827</v>
+        <v>477929</v>
       </c>
       <c r="R7" t="n">
-        <v>6601000</v>
+        <v>6600947</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1416,7 +1411,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1426,7 +1421,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1584,7 +1579,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124893662</v>
+        <v>124893452</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1634,7 +1629,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1678,7 +1673,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1688,7 +1683,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1715,7 +1710,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124893740</v>
+        <v>124893715</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1774,10 +1769,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477877</v>
+        <v>477879</v>
       </c>
       <c r="R10" t="n">
-        <v>6600884</v>
+        <v>6600886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1846,7 +1841,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124891352</v>
+        <v>124891336</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1896,7 +1891,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1905,10 +1900,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477836</v>
+        <v>477824</v>
       </c>
       <c r="R11" t="n">
-        <v>6601000</v>
+        <v>6601003</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,7 +1935,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1950,7 +1945,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Tappade yttre vingpennor, slagsmål?</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124893715</v>
+        <v>124893740</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477879</v>
+        <v>477877</v>
       </c>
       <c r="R13" t="n">
-        <v>6600886</v>
+        <v>6600884</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -792,14 +792,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124891352</v>
+        <v>124893491</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -842,19 +842,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477836</v>
+        <v>477909</v>
       </c>
       <c r="R3" t="n">
-        <v>6601000</v>
+        <v>6600929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,14 +923,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124891215</v>
+        <v>124892467</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -973,19 +973,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477827</v>
+        <v>477876</v>
       </c>
       <c r="R4" t="n">
-        <v>6601000</v>
+        <v>6601108</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,14 +1054,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124892509</v>
+        <v>124892723</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477884</v>
+        <v>477910</v>
       </c>
       <c r="R5" t="n">
-        <v>6601095</v>
+        <v>6601063</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,14 +1185,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124893754</v>
+        <v>124892509</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1235,20 +1235,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477867</v>
+        <v>477884</v>
       </c>
       <c r="R6" t="n">
-        <v>6600886</v>
+        <v>6601095</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1290,7 +1289,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,14 +1316,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124893402</v>
+        <v>124893740</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1367,19 +1366,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477929</v>
+        <v>477877</v>
       </c>
       <c r="R7" t="n">
-        <v>6600947</v>
+        <v>6600884</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1421,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,14 +1447,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124892723</v>
+        <v>124893754</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1501,16 +1500,17 @@
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477910</v>
+        <v>477867</v>
       </c>
       <c r="R8" t="n">
-        <v>6601063</v>
+        <v>6600886</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,14 +1579,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124893452</v>
+        <v>124891215</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1629,19 +1629,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477909</v>
+        <v>477827</v>
       </c>
       <c r="R9" t="n">
-        <v>6600929</v>
+        <v>6601000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,14 +1710,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124893715</v>
+        <v>124893402</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1760,19 +1760,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477879</v>
+        <v>477929</v>
       </c>
       <c r="R10" t="n">
-        <v>6600886</v>
+        <v>6600947</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1977,14 +1977,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124892467</v>
+        <v>124891352</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2032,14 +2032,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477876</v>
+        <v>477836</v>
       </c>
       <c r="R12" t="n">
-        <v>6601108</v>
+        <v>6601000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2108,14 +2108,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124893740</v>
+        <v>124893715</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477877</v>
+        <v>477879</v>
       </c>
       <c r="R13" t="n">
-        <v>6600884</v>
+        <v>6600886</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124893491</v>
+        <v>124893754</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -845,16 +845,17 @@
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477909</v>
+        <v>477867</v>
       </c>
       <c r="R3" t="n">
-        <v>6600929</v>
+        <v>6600886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,14 +924,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124892467</v>
+        <v>124892723</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -973,7 +974,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,10 +983,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477876</v>
+        <v>477910</v>
       </c>
       <c r="R4" t="n">
-        <v>6601108</v>
+        <v>6601063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1055,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124892723</v>
+        <v>124893662</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1113,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477910</v>
+        <v>477909</v>
       </c>
       <c r="R5" t="n">
-        <v>6601063</v>
+        <v>6600929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,14 +1186,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124892509</v>
+        <v>124891215</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1235,19 +1236,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477884</v>
+        <v>477827</v>
       </c>
       <c r="R6" t="n">
-        <v>6601095</v>
+        <v>6601000</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1280,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1290,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1447,14 +1448,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124893754</v>
+        <v>124893715</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1497,17 +1498,16 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477867</v>
+        <v>477879</v>
       </c>
       <c r="R8" t="n">
         <v>6600886</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,14 +1579,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891215</v>
+        <v>124891352</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1629,7 +1629,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1638,7 +1638,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477827</v>
+        <v>477836</v>
       </c>
       <c r="R9" t="n">
         <v>6601000</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,14 +1710,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124893402</v>
+        <v>124892467</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477929</v>
+        <v>477876</v>
       </c>
       <c r="R10" t="n">
-        <v>6600947</v>
+        <v>6601108</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1841,14 +1841,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124891336</v>
+        <v>124892509</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1891,19 +1891,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477824</v>
+        <v>477884</v>
       </c>
       <c r="R11" t="n">
-        <v>6601003</v>
+        <v>6601095</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1945,12 +1945,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Tappade yttre vingpennor, slagsmål?</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1977,14 +1972,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891352</v>
+        <v>124893402</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2027,19 +2022,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477836</v>
+        <v>477929</v>
       </c>
       <c r="R12" t="n">
-        <v>6601000</v>
+        <v>6600947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,7 +2066,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2081,7 +2076,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2108,14 +2103,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124893715</v>
+        <v>124891336</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2158,7 +2153,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2167,10 +2162,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477879</v>
+        <v>477824</v>
       </c>
       <c r="R13" t="n">
-        <v>6600886</v>
+        <v>6601003</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2202,7 +2197,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2212,7 +2207,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Tappade yttre vingpennor, slagsmål?</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -792,14 +792,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124893754</v>
+        <v>124892509</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -842,20 +842,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477867</v>
+        <v>477884</v>
       </c>
       <c r="R3" t="n">
-        <v>6600886</v>
+        <v>6601095</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124892723</v>
+        <v>124893754</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -977,16 +976,17 @@
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477910</v>
+        <v>477867</v>
       </c>
       <c r="R4" t="n">
-        <v>6601063</v>
+        <v>6600886</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,7 +1055,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893662</v>
+        <v>124893402</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477909</v>
+        <v>477929</v>
       </c>
       <c r="R5" t="n">
-        <v>6600929</v>
+        <v>6600947</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1186,7 +1186,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124891215</v>
+        <v>124893662</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1241,14 +1241,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477827</v>
+        <v>477909</v>
       </c>
       <c r="R6" t="n">
-        <v>6601000</v>
+        <v>6600929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124893740</v>
+        <v>124892467</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1372,14 +1372,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477877</v>
+        <v>477876</v>
       </c>
       <c r="R7" t="n">
-        <v>6600884</v>
+        <v>6601108</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1579,7 +1579,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891352</v>
+        <v>124893740</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477836</v>
+        <v>477877</v>
       </c>
       <c r="R9" t="n">
-        <v>6601000</v>
+        <v>6600884</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,14 +1710,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124892467</v>
+        <v>124891215</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1760,19 +1760,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477876</v>
+        <v>477827</v>
       </c>
       <c r="R10" t="n">
-        <v>6601108</v>
+        <v>6601000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1841,14 +1841,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124892509</v>
+        <v>124892723</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477884</v>
+        <v>477910</v>
       </c>
       <c r="R11" t="n">
-        <v>6601095</v>
+        <v>6601063</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1972,14 +1972,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124893402</v>
+        <v>124891352</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2022,19 +2022,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477929</v>
+        <v>477836</v>
       </c>
       <c r="R12" t="n">
-        <v>6600947</v>
+        <v>6601000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893402</v>
+        <v>124893662</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477929</v>
+        <v>477909</v>
       </c>
       <c r="R5" t="n">
-        <v>6600947</v>
+        <v>6600929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1186,7 +1186,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124893662</v>
+        <v>124893402</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477909</v>
+        <v>477929</v>
       </c>
       <c r="R6" t="n">
-        <v>6600929</v>
+        <v>6600947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -1055,7 +1055,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893662</v>
+        <v>124893402</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477909</v>
+        <v>477929</v>
       </c>
       <c r="R5" t="n">
-        <v>6600929</v>
+        <v>6600947</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1186,7 +1186,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124893402</v>
+        <v>124893662</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477929</v>
+        <v>477909</v>
       </c>
       <c r="R6" t="n">
-        <v>6600947</v>
+        <v>6600929</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -792,14 +792,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124892509</v>
+        <v>124893662</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477884</v>
+        <v>477909</v>
       </c>
       <c r="R3" t="n">
-        <v>6601095</v>
+        <v>6600929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124893754</v>
+        <v>124892723</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -976,17 +976,16 @@
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477867</v>
+        <v>477910</v>
       </c>
       <c r="R4" t="n">
-        <v>6600886</v>
+        <v>6601063</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,7 +1054,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893402</v>
+        <v>124893754</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1108,16 +1107,17 @@
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477929</v>
+        <v>477867</v>
       </c>
       <c r="R5" t="n">
-        <v>6600947</v>
+        <v>6600886</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1186,14 +1186,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124893662</v>
+        <v>124892467</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477909</v>
+        <v>477876</v>
       </c>
       <c r="R6" t="n">
-        <v>6600929</v>
+        <v>6601108</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124892467</v>
+        <v>124893740</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1372,14 +1372,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477876</v>
+        <v>477877</v>
       </c>
       <c r="R7" t="n">
-        <v>6601108</v>
+        <v>6600884</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,14 +1448,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124893715</v>
+        <v>124891215</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477879</v>
+        <v>477827</v>
       </c>
       <c r="R8" t="n">
-        <v>6600886</v>
+        <v>6601000</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,7 +1579,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124893740</v>
+        <v>124891352</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477877</v>
+        <v>477836</v>
       </c>
       <c r="R9" t="n">
-        <v>6600884</v>
+        <v>6601000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1673,7 +1673,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,14 +1710,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124891215</v>
+        <v>124892509</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1760,19 +1760,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477827</v>
+        <v>477884</v>
       </c>
       <c r="R10" t="n">
-        <v>6601000</v>
+        <v>6601095</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1841,7 +1841,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124892723</v>
+        <v>124893402</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477910</v>
+        <v>477929</v>
       </c>
       <c r="R11" t="n">
-        <v>6601063</v>
+        <v>6600947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1972,7 +1972,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891352</v>
+        <v>124893715</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477836</v>
+        <v>477879</v>
       </c>
       <c r="R12" t="n">
-        <v>6601000</v>
+        <v>6600886</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124893662</v>
+        <v>124891336</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -842,19 +842,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477909</v>
+        <v>477824</v>
       </c>
       <c r="R3" t="n">
-        <v>6600929</v>
+        <v>6601003</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tappade yttre vingpennor, slagsmål?</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124892723</v>
+        <v>124891215</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -978,14 +983,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477910</v>
+        <v>477827</v>
       </c>
       <c r="R4" t="n">
-        <v>6601063</v>
+        <v>6601000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,14 +1059,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893754</v>
+        <v>124891352</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1104,20 +1109,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477867</v>
+        <v>477836</v>
       </c>
       <c r="R5" t="n">
-        <v>6600886</v>
+        <v>6601000</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1153,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1163,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1186,7 +1190,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124892467</v>
+        <v>124893715</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1241,14 +1245,14 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477876</v>
+        <v>477879</v>
       </c>
       <c r="R6" t="n">
-        <v>6601108</v>
+        <v>6600886</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1280,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1290,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,14 +1321,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124893740</v>
+        <v>124893491</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1367,19 +1371,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477877</v>
+        <v>477909</v>
       </c>
       <c r="R7" t="n">
-        <v>6600884</v>
+        <v>6600929</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1415,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1421,7 +1425,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,14 +1452,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124891215</v>
+        <v>124893740</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1498,7 +1502,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,10 +1511,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477827</v>
+        <v>477877</v>
       </c>
       <c r="R8" t="n">
-        <v>6601000</v>
+        <v>6600884</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1546,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1556,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,14 +1583,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891352</v>
+        <v>124893754</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1629,19 +1633,20 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477836</v>
+        <v>477867</v>
       </c>
       <c r="R9" t="n">
-        <v>6601000</v>
+        <v>6600886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1673,7 +1678,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1683,7 +1688,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,14 +1715,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124892509</v>
+        <v>124892723</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1760,7 +1765,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1769,10 +1774,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477884</v>
+        <v>477910</v>
       </c>
       <c r="R10" t="n">
-        <v>6601095</v>
+        <v>6601063</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1819,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1841,14 +1846,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124893402</v>
+        <v>124892467</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1891,7 +1896,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1900,10 +1905,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477929</v>
+        <v>477876</v>
       </c>
       <c r="R11" t="n">
-        <v>6600947</v>
+        <v>6601108</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1935,7 +1940,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1945,7 +1950,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1972,7 +1977,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124893715</v>
+        <v>124892509</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -2027,14 +2032,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477879</v>
+        <v>477884</v>
       </c>
       <c r="R12" t="n">
-        <v>6600886</v>
+        <v>6601095</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2066,7 +2071,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2076,7 +2081,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2103,7 +2108,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124891336</v>
+        <v>124893402</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2153,19 +2158,19 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477824</v>
+        <v>477929</v>
       </c>
       <c r="R13" t="n">
-        <v>6601003</v>
+        <v>6600947</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2197,7 +2202,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2207,12 +2212,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Tappade yttre vingpennor, slagsmål?</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -928,7 +928,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124891215</v>
+        <v>124893662</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -983,14 +983,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477827</v>
+        <v>477909</v>
       </c>
       <c r="R4" t="n">
-        <v>6601000</v>
+        <v>6600929</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1059,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124891352</v>
+        <v>124893740</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1118,10 +1118,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477836</v>
+        <v>477877</v>
       </c>
       <c r="R5" t="n">
-        <v>6601000</v>
+        <v>6600884</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,7 +1153,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,7 +1190,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124893715</v>
+        <v>124891352</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477879</v>
+        <v>477836</v>
       </c>
       <c r="R6" t="n">
-        <v>6600886</v>
+        <v>6601000</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1321,14 +1321,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124893491</v>
+        <v>124892467</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477909</v>
+        <v>477876</v>
       </c>
       <c r="R7" t="n">
-        <v>6600929</v>
+        <v>6601108</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1452,7 +1452,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124893740</v>
+        <v>124892509</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1507,14 +1507,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477877</v>
+        <v>477884</v>
       </c>
       <c r="R8" t="n">
-        <v>6600884</v>
+        <v>6601095</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,14 +1583,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124893754</v>
+        <v>124893715</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1633,17 +1633,16 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477867</v>
+        <v>477879</v>
       </c>
       <c r="R9" t="n">
         <v>6600886</v>
@@ -1678,7 +1677,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1688,7 +1687,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1846,14 +1845,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124892467</v>
+        <v>124893402</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1896,7 +1895,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1905,10 +1904,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477876</v>
+        <v>477929</v>
       </c>
       <c r="R11" t="n">
-        <v>6601108</v>
+        <v>6600947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1950,7 +1949,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1977,14 +1976,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124892509</v>
+        <v>124893754</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2027,19 +2026,20 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477884</v>
+        <v>477867</v>
       </c>
       <c r="R12" t="n">
-        <v>6601095</v>
+        <v>6600886</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124893402</v>
+        <v>124891215</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2163,14 +2163,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477929</v>
+        <v>477827</v>
       </c>
       <c r="R13" t="n">
-        <v>6600947</v>
+        <v>6601000</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124891336</v>
+        <v>124893754</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -842,19 +842,20 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477824</v>
+        <v>477867</v>
       </c>
       <c r="R3" t="n">
-        <v>6601003</v>
+        <v>6600886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +887,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,12 +897,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tappade yttre vingpennor, slagsmål?</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,14 +924,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124893662</v>
+        <v>124893740</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -978,19 +974,19 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477909</v>
+        <v>477877</v>
       </c>
       <c r="R4" t="n">
-        <v>6600929</v>
+        <v>6600884</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1022,7 +1018,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1032,7 +1028,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1055,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893740</v>
+        <v>124891352</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1118,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477877</v>
+        <v>477836</v>
       </c>
       <c r="R5" t="n">
-        <v>6600884</v>
+        <v>6601000</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,14 +1186,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124891352</v>
+        <v>124893402</v>
       </c>
       <c r="B6" t="n">
         <v>56722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1240,19 +1236,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477836</v>
+        <v>477929</v>
       </c>
       <c r="R6" t="n">
-        <v>6601000</v>
+        <v>6600947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1280,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1290,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1321,14 +1317,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124892467</v>
+        <v>124893491</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1371,7 +1367,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1380,10 +1376,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477876</v>
+        <v>477909</v>
       </c>
       <c r="R7" t="n">
-        <v>6601108</v>
+        <v>6600929</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,7 +1411,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1425,7 +1421,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1452,7 +1448,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124892509</v>
+        <v>124892467</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1511,10 +1507,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477884</v>
+        <v>477876</v>
       </c>
       <c r="R8" t="n">
-        <v>6601095</v>
+        <v>6601108</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1556,7 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,7 +1579,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124893715</v>
+        <v>124892509</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
@@ -1638,14 +1634,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477879</v>
+        <v>477884</v>
       </c>
       <c r="R9" t="n">
-        <v>6600886</v>
+        <v>6601095</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1677,7 +1673,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1687,7 +1683,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1845,7 +1841,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124893402</v>
+        <v>124891215</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
@@ -1900,14 +1896,14 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477929</v>
+        <v>477827</v>
       </c>
       <c r="R11" t="n">
-        <v>6600947</v>
+        <v>6601000</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1939,7 +1935,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,7 +1945,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1976,7 +1972,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124893754</v>
+        <v>124891336</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -2026,20 +2022,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477867</v>
+        <v>477824</v>
       </c>
       <c r="R12" t="n">
-        <v>6600886</v>
+        <v>6601003</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,7 +2066,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2081,7 +2076,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Tappade yttre vingpennor, slagsmål?</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2108,14 +2108,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124891215</v>
+        <v>124893715</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477827</v>
+        <v>477879</v>
       </c>
       <c r="R13" t="n">
-        <v>6601000</v>
+        <v>6600886</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124893754</v>
+        <v>124893491</v>
       </c>
       <c r="B3" t="n">
         <v>56722</v>
@@ -845,17 +845,16 @@
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477867</v>
+        <v>477909</v>
       </c>
       <c r="R3" t="n">
-        <v>6600886</v>
+        <v>6600929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +923,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124893740</v>
+        <v>124892467</v>
       </c>
       <c r="B4" t="n">
         <v>56722</v>
@@ -979,14 +978,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477877</v>
+        <v>477876</v>
       </c>
       <c r="R4" t="n">
-        <v>6600884</v>
+        <v>6601108</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1018,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1028,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1055,7 +1054,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124891352</v>
+        <v>124893740</v>
       </c>
       <c r="B5" t="n">
         <v>56722</v>
@@ -1114,10 +1113,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477836</v>
+        <v>477877</v>
       </c>
       <c r="R5" t="n">
-        <v>6601000</v>
+        <v>6600884</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1148,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1158,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1317,7 +1316,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124893491</v>
+        <v>124892723</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1376,10 +1375,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477909</v>
+        <v>477910</v>
       </c>
       <c r="R7" t="n">
-        <v>6600929</v>
+        <v>6601063</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1411,7 +1410,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1421,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1448,7 +1447,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124892467</v>
+        <v>124893715</v>
       </c>
       <c r="B8" t="n">
         <v>56722</v>
@@ -1503,14 +1502,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477876</v>
+        <v>477879</v>
       </c>
       <c r="R8" t="n">
-        <v>6601108</v>
+        <v>6600886</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1542,7 +1541,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1551,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,14 +1578,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124892509</v>
+        <v>124891336</v>
       </c>
       <c r="B9" t="n">
         <v>56722</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1629,19 +1628,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477884</v>
+        <v>477824</v>
       </c>
       <c r="R9" t="n">
-        <v>6601095</v>
+        <v>6601003</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1673,7 +1672,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1683,7 +1682,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tappade yttre vingpennor, slagsmål?</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,7 +1714,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124892723</v>
+        <v>124893754</v>
       </c>
       <c r="B10" t="n">
         <v>56722</v>
@@ -1763,16 +1767,17 @@
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477910</v>
+        <v>477867</v>
       </c>
       <c r="R10" t="n">
-        <v>6601063</v>
+        <v>6600886</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1819,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1841,14 +1846,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124891215</v>
+        <v>124892509</v>
       </c>
       <c r="B11" t="n">
         <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1891,19 +1896,19 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477827</v>
+        <v>477884</v>
       </c>
       <c r="R11" t="n">
-        <v>6601000</v>
+        <v>6601095</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1935,7 +1940,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1945,7 +1950,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1972,7 +1977,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891336</v>
+        <v>124891215</v>
       </c>
       <c r="B12" t="n">
         <v>56722</v>
@@ -2022,7 +2027,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2031,10 +2036,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477824</v>
+        <v>477827</v>
       </c>
       <c r="R12" t="n">
-        <v>6601003</v>
+        <v>6601000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2066,7 +2071,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2076,12 +2081,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Tappade yttre vingpennor, slagsmål?</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2108,7 +2108,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124893715</v>
+        <v>124891352</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477879</v>
+        <v>477836</v>
       </c>
       <c r="R13" t="n">
-        <v>6600886</v>
+        <v>6601000</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124892816</v>
       </c>
       <c r="B2" t="n">
-        <v>79920</v>
+        <v>80057</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -792,14 +792,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124893491</v>
+        <v>124891352</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -842,19 +842,19 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477909</v>
+        <v>477836</v>
       </c>
       <c r="R3" t="n">
-        <v>6600929</v>
+        <v>6601000</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124892467</v>
+        <v>124893740</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -978,14 +978,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477876</v>
+        <v>477877</v>
       </c>
       <c r="R4" t="n">
-        <v>6601108</v>
+        <v>6600884</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,14 +1054,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893740</v>
+        <v>124893491</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1104,19 +1104,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477877</v>
+        <v>477909</v>
       </c>
       <c r="R5" t="n">
-        <v>6600884</v>
+        <v>6600929</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,10 +1185,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124893402</v>
+        <v>124891336</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1235,19 +1235,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477929</v>
+        <v>477824</v>
       </c>
       <c r="R6" t="n">
-        <v>6600947</v>
+        <v>6601003</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1289,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Tappade yttre vingpennor, slagsmål?</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1319,7 +1324,7 @@
         <v>124892723</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1447,14 +1452,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124893715</v>
+        <v>124893754</v>
       </c>
       <c r="B8" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1497,16 +1502,17 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477879</v>
+        <v>477867</v>
       </c>
       <c r="R8" t="n">
         <v>6600886</v>
@@ -1541,7 +1547,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1551,7 +1557,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1578,10 +1584,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891336</v>
+        <v>124891215</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1628,7 +1634,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1637,10 +1643,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477824</v>
+        <v>477827</v>
       </c>
       <c r="R9" t="n">
-        <v>6601003</v>
+        <v>6601000</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1672,7 +1678,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1682,12 +1688,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Tappade yttre vingpennor, slagsmål?</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1714,14 +1715,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124893754</v>
+        <v>124892509</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1764,20 +1765,19 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477867</v>
+        <v>477884</v>
       </c>
       <c r="R10" t="n">
-        <v>6600886</v>
+        <v>6601095</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1846,14 +1846,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124892509</v>
+        <v>124893402</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477884</v>
+        <v>477929</v>
       </c>
       <c r="R11" t="n">
-        <v>6601095</v>
+        <v>6600947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1977,14 +1977,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891215</v>
+        <v>124892467</v>
       </c>
       <c r="B12" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2027,19 +2027,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477827</v>
+        <v>477876</v>
       </c>
       <c r="R12" t="n">
-        <v>6601000</v>
+        <v>6601108</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124891352</v>
+        <v>124893715</v>
       </c>
       <c r="B13" t="n">
-        <v>56722</v>
+        <v>56836</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2167,10 +2167,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>477836</v>
+        <v>477879</v>
       </c>
       <c r="R13" t="n">
-        <v>6601000</v>
+        <v>6600886</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124891352</v>
+        <v>124893452</v>
       </c>
       <c r="B3" t="n">
         <v>56836</v>
@@ -847,14 +847,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>477836</v>
+        <v>477909</v>
       </c>
       <c r="R3" t="n">
-        <v>6601000</v>
+        <v>6600929</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,14 +923,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124893740</v>
+        <v>124891336</v>
       </c>
       <c r="B4" t="n">
         <v>56836</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,10 +982,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477877</v>
+        <v>477824</v>
       </c>
       <c r="R4" t="n">
-        <v>6600884</v>
+        <v>6601003</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1017,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,7 +1027,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tappade yttre vingpennor, slagsmål?</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,14 +1059,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893491</v>
+        <v>124893740</v>
       </c>
       <c r="B5" t="n">
         <v>56836</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1104,19 +1109,19 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477909</v>
+        <v>477877</v>
       </c>
       <c r="R5" t="n">
-        <v>6600929</v>
+        <v>6600884</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1148,7 +1153,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1158,7 +1163,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1185,7 +1190,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124891336</v>
+        <v>124893402</v>
       </c>
       <c r="B6" t="n">
         <v>56836</v>
@@ -1235,19 +1240,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477824</v>
+        <v>477929</v>
       </c>
       <c r="R6" t="n">
-        <v>6601003</v>
+        <v>6600947</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,12 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Tappade yttre vingpennor, slagsmål?</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1452,14 +1452,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124893754</v>
+        <v>124892509</v>
       </c>
       <c r="B8" t="n">
         <v>56836</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1502,20 +1502,19 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477867</v>
+        <v>477884</v>
       </c>
       <c r="R8" t="n">
-        <v>6600886</v>
+        <v>6601095</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1547,7 +1546,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1557,7 +1556,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,7 +1583,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124891215</v>
+        <v>124893754</v>
       </c>
       <c r="B9" t="n">
         <v>56836</v>
@@ -1637,16 +1636,17 @@
           <t>färsk spillning</t>
         </is>
       </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477827</v>
+        <v>477867</v>
       </c>
       <c r="R9" t="n">
-        <v>6601000</v>
+        <v>6600886</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1715,7 +1715,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124892509</v>
+        <v>124891352</v>
       </c>
       <c r="B10" t="n">
         <v>56836</v>
@@ -1770,14 +1770,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477884</v>
+        <v>477836</v>
       </c>
       <c r="R10" t="n">
-        <v>6601095</v>
+        <v>6601000</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1846,14 +1846,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124893402</v>
+        <v>124892467</v>
       </c>
       <c r="B11" t="n">
         <v>56836</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>477929</v>
+        <v>477876</v>
       </c>
       <c r="R11" t="n">
-        <v>6600947</v>
+        <v>6601108</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1977,14 +1977,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124892467</v>
+        <v>124891215</v>
       </c>
       <c r="B12" t="n">
         <v>56836</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Behöver inte valideras</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2027,19 +2027,19 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477876</v>
+        <v>477827</v>
       </c>
       <c r="R12" t="n">
-        <v>6601108</v>
+        <v>6601000</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,7 +2071,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 21848-2025 artfynd.xlsx
+++ b/artfynd/A 21848-2025 artfynd.xlsx
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>80057</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>LC</t>
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124893452</v>
+        <v>124893662</v>
       </c>
       <c r="B3" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -842,7 +832,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -886,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +886,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:07</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124891336</v>
+        <v>124891215</v>
       </c>
       <c r="B4" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +958,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -982,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>477824</v>
+        <v>477827</v>
       </c>
       <c r="R4" t="n">
-        <v>6601003</v>
+        <v>6601000</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1017,7 +1002,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1027,12 +1012,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Tappade yttre vingpennor, slagsmål?</t>
+          <t>11:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,15 +1039,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124893740</v>
+        <v>124893754</v>
       </c>
       <c r="B5" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,19 +1084,20 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>477877</v>
+        <v>477867</v>
       </c>
       <c r="R5" t="n">
-        <v>6600884</v>
+        <v>6600886</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1153,7 +1129,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1163,7 +1139,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,15 +1166,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124893402</v>
+        <v>124893740</v>
       </c>
       <c r="B6" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1240,19 +1211,19 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>477929</v>
+        <v>477877</v>
       </c>
       <c r="R6" t="n">
-        <v>6600947</v>
+        <v>6600884</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1255,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1265,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1321,15 +1292,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124892723</v>
+        <v>124891352</v>
       </c>
       <c r="B7" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1371,19 +1337,19 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Florinna, Grythyttans sn, Vstm</t>
+          <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>477910</v>
+        <v>477836</v>
       </c>
       <c r="R7" t="n">
-        <v>6601063</v>
+        <v>6601000</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1415,7 +1381,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1425,7 +1391,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1452,15 +1418,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124892509</v>
+        <v>124893402</v>
       </c>
       <c r="B8" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1502,7 +1463,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1511,10 +1472,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>477884</v>
+        <v>477929</v>
       </c>
       <c r="R8" t="n">
-        <v>6601095</v>
+        <v>6600947</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1546,7 +1507,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1556,7 +1517,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1583,15 +1544,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124893754</v>
+        <v>124891336</v>
       </c>
       <c r="B9" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1633,20 +1589,19 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Krontorp, Krontorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>477867</v>
+        <v>477824</v>
       </c>
       <c r="R9" t="n">
-        <v>6600886</v>
+        <v>6601003</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1633,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1688,7 +1643,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Tappade yttre vingpennor, slagsmål?</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1715,15 +1675,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124891352</v>
+        <v>124892509</v>
       </c>
       <c r="B10" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1770,14 +1725,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>477836</v>
+        <v>477884</v>
       </c>
       <c r="R10" t="n">
-        <v>6601000</v>
+        <v>6601095</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1809,7 +1764,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,7 +1774,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1849,12 +1804,7 @@
         <v>124892467</v>
       </c>
       <c r="B11" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1977,15 +1927,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124891215</v>
+        <v>124892723</v>
       </c>
       <c r="B12" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2032,14 +1977,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Krontorp, Krontorp, Vstm</t>
+          <t>Florinna, Grythyttans sn, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>477827</v>
+        <v>477910</v>
       </c>
       <c r="R12" t="n">
-        <v>6601000</v>
+        <v>6601063</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2071,7 +2016,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2081,7 +2026,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:46</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2111,12 +2056,7 @@
         <v>124893715</v>
       </c>
       <c r="B13" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>56843</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
